--- a/Pruebas calificadas/COLEGIO-EL-ENSUEÑO-(IED)-302_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-ENSUEÑO-(IED)-302_CALIFICADO.xlsx
@@ -759,7 +759,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1774,7 +1774,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1977,7 +1977,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2180,7 +2180,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2383,7 +2383,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2789,7 +2789,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3195,7 +3195,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3398,7 +3398,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3804,7 +3804,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -4007,7 +4007,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4413,7 +4413,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4819,7 +4819,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5225,7 +5225,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5428,7 +5428,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5631,7 +5631,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5834,7 +5834,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6443,7 +6443,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6849,7 +6849,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7052,7 +7052,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7255,7 +7255,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7458,7 +7458,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7661,7 +7661,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7864,7 +7864,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8067,7 +8067,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8270,7 +8270,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8473,7 +8473,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8668,7 +8668,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8819,7 +8819,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9022,7 +9022,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9225,7 +9225,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9428,7 +9428,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9631,7 +9631,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10037,7 +10037,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10240,7 +10240,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10646,7 +10646,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10849,7 +10849,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11052,7 +11052,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11255,7 +11255,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11458,7 +11458,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11661,7 +11661,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11864,7 +11864,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12067,7 +12067,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12473,7 +12473,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12676,7 +12676,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12879,7 +12879,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13082,7 +13082,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13285,7 +13285,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13691,7 +13691,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13894,7 +13894,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14097,7 +14097,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14300,7 +14300,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14503,7 +14503,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14706,7 +14706,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14909,7 +14909,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15112,7 +15112,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -15315,7 +15315,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -15518,7 +15518,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -15721,7 +15721,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -15924,7 +15924,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -16127,7 +16127,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -16330,7 +16330,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -16533,7 +16533,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -16720,7 +16720,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
+          <t>COLEGIO EL ENSUEÑO (IED)</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">

--- a/Pruebas calificadas/COLEGIO-EL-ENSUEÑO-(IED)-302_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO-EL-ENSUEÑO-(IED)-302_CALIFICADO.xlsx
@@ -747,11 +747,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -759,7 +755,7 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
@@ -950,11 +946,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -962,7 +954,7 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
@@ -1153,11 +1145,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1165,7 +1153,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -1356,11 +1344,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1368,7 +1352,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1559,11 +1543,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1571,7 +1551,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1762,11 +1742,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1774,7 +1750,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1965,11 +1941,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -1977,7 +1949,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -2168,11 +2140,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2180,7 +2148,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -2371,11 +2339,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2383,7 +2347,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -2574,11 +2538,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2586,7 +2546,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -2777,11 +2737,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2789,7 +2745,7 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
@@ -2980,11 +2936,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -2992,7 +2944,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -3183,11 +3135,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3195,7 +3143,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -3386,11 +3334,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3398,7 +3342,7 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
@@ -3589,11 +3533,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3601,7 +3541,7 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
@@ -3792,11 +3732,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -3804,7 +3740,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -3995,11 +3931,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4007,7 +3939,7 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
@@ -4198,11 +4130,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4210,7 +4138,7 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
@@ -4401,11 +4329,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4413,7 +4337,7 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
@@ -4604,11 +4528,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4616,7 +4536,7 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
@@ -4807,11 +4727,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -4819,7 +4735,7 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D22" s="2" t="inlineStr">
@@ -5010,11 +4926,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5022,7 +4934,7 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
@@ -5213,11 +5125,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5225,7 +5133,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -5416,11 +5324,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5428,7 +5332,7 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
@@ -5619,11 +5523,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5631,7 +5531,7 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
@@ -5822,11 +5722,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -5834,7 +5730,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -6025,11 +5921,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6037,7 +5929,7 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
@@ -6228,11 +6120,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6240,7 +6128,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
@@ -6431,11 +6319,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6443,7 +6327,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
@@ -6634,11 +6518,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6646,7 +6526,7 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
@@ -6837,11 +6717,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -6849,7 +6725,7 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
@@ -7040,11 +6916,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7052,7 +6924,7 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
@@ -7243,11 +7115,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7255,7 +7123,7 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
@@ -7446,11 +7314,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7458,7 +7322,7 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
@@ -7649,11 +7513,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7661,7 +7521,7 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D36" s="2" t="inlineStr">
@@ -7852,11 +7712,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -7864,7 +7720,7 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
@@ -8055,11 +7911,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8067,7 +7919,7 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
@@ -8258,11 +8110,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8270,7 +8118,7 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
@@ -8461,11 +8309,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8473,7 +8317,7 @@
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
@@ -8656,11 +8500,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8668,7 +8508,7 @@
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
@@ -8807,11 +8647,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -8819,7 +8655,7 @@
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
@@ -9010,11 +8846,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9022,7 +8854,7 @@
       </c>
       <c r="C43" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D43" s="2" t="inlineStr">
@@ -9213,11 +9045,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9225,7 +9053,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -9416,11 +9244,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9428,7 +9252,7 @@
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
@@ -9619,11 +9443,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9631,7 +9451,7 @@
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
@@ -9822,11 +9642,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -9834,7 +9650,7 @@
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
@@ -10025,11 +9841,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10037,7 +9849,7 @@
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
@@ -10228,11 +10040,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10240,7 +10048,7 @@
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
@@ -10431,11 +10239,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10443,7 +10247,7 @@
       </c>
       <c r="C50" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D50" s="2" t="inlineStr">
@@ -10634,11 +10438,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10646,7 +10446,7 @@
       </c>
       <c r="C51" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D51" s="2" t="inlineStr">
@@ -10837,11 +10637,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -10849,7 +10645,7 @@
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
@@ -11040,11 +10836,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11052,7 +10844,7 @@
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
@@ -11243,11 +11035,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11255,7 +11043,7 @@
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
@@ -11446,11 +11234,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11458,7 +11242,7 @@
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
@@ -11649,11 +11433,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11661,7 +11441,7 @@
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
@@ -11852,11 +11632,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -11864,7 +11640,7 @@
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
@@ -12055,11 +11831,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12067,7 +11839,7 @@
       </c>
       <c r="C58" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D58" s="2" t="inlineStr">
@@ -12258,11 +12030,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12270,7 +12038,7 @@
       </c>
       <c r="C59" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D59" s="2" t="inlineStr">
@@ -12461,11 +12229,7 @@
       </c>
     </row>
     <row r="60">
-      <c r="A60" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A60" s="2" t="inlineStr"/>
       <c r="B60" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12473,7 +12237,7 @@
       </c>
       <c r="C60" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D60" s="2" t="inlineStr">
@@ -12664,11 +12428,7 @@
       </c>
     </row>
     <row r="61">
-      <c r="A61" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A61" s="2" t="inlineStr"/>
       <c r="B61" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12676,7 +12436,7 @@
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
@@ -12867,11 +12627,7 @@
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A62" s="2" t="inlineStr"/>
       <c r="B62" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -12879,7 +12635,7 @@
       </c>
       <c r="C62" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D62" s="2" t="inlineStr">
@@ -13070,11 +12826,7 @@
       </c>
     </row>
     <row r="63">
-      <c r="A63" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A63" s="2" t="inlineStr"/>
       <c r="B63" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13082,7 +12834,7 @@
       </c>
       <c r="C63" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D63" s="2" t="inlineStr">
@@ -13273,11 +13025,7 @@
       </c>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A64" s="2" t="inlineStr"/>
       <c r="B64" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13285,7 +13033,7 @@
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
@@ -13476,11 +13224,7 @@
       </c>
     </row>
     <row r="65">
-      <c r="A65" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A65" s="2" t="inlineStr"/>
       <c r="B65" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13488,7 +13232,7 @@
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
@@ -13679,11 +13423,7 @@
       </c>
     </row>
     <row r="66">
-      <c r="A66" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A66" s="2" t="inlineStr"/>
       <c r="B66" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13691,7 +13431,7 @@
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
@@ -13882,11 +13622,7 @@
       </c>
     </row>
     <row r="67">
-      <c r="A67" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A67" s="2" t="inlineStr"/>
       <c r="B67" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -13894,7 +13630,7 @@
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
@@ -14085,11 +13821,7 @@
       </c>
     </row>
     <row r="68">
-      <c r="A68" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A68" s="2" t="inlineStr"/>
       <c r="B68" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14097,7 +13829,7 @@
       </c>
       <c r="C68" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D68" s="2" t="inlineStr">
@@ -14288,11 +14020,7 @@
       </c>
     </row>
     <row r="69">
-      <c r="A69" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A69" s="2" t="inlineStr"/>
       <c r="B69" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14300,7 +14028,7 @@
       </c>
       <c r="C69" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D69" s="2" t="inlineStr">
@@ -14491,11 +14219,7 @@
       </c>
     </row>
     <row r="70">
-      <c r="A70" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A70" s="2" t="inlineStr"/>
       <c r="B70" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14503,7 +14227,7 @@
       </c>
       <c r="C70" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D70" s="2" t="inlineStr">
@@ -14694,11 +14418,7 @@
       </c>
     </row>
     <row r="71">
-      <c r="A71" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A71" s="2" t="inlineStr"/>
       <c r="B71" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14706,7 +14426,7 @@
       </c>
       <c r="C71" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D71" s="2" t="inlineStr">
@@ -14897,11 +14617,7 @@
       </c>
     </row>
     <row r="72">
-      <c r="A72" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A72" s="2" t="inlineStr"/>
       <c r="B72" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -14909,7 +14625,7 @@
       </c>
       <c r="C72" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D72" s="2" t="inlineStr">
@@ -15100,11 +14816,7 @@
       </c>
     </row>
     <row r="73">
-      <c r="A73" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A73" s="2" t="inlineStr"/>
       <c r="B73" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15112,7 +14824,7 @@
       </c>
       <c r="C73" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D73" s="2" t="inlineStr">
@@ -15303,11 +15015,7 @@
       </c>
     </row>
     <row r="74">
-      <c r="A74" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A74" s="2" t="inlineStr"/>
       <c r="B74" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15315,7 +15023,7 @@
       </c>
       <c r="C74" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D74" s="2" t="inlineStr">
@@ -15506,11 +15214,7 @@
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A75" s="2" t="inlineStr"/>
       <c r="B75" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15518,7 +15222,7 @@
       </c>
       <c r="C75" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D75" s="2" t="inlineStr">
@@ -15709,11 +15413,7 @@
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A76" s="2" t="inlineStr"/>
       <c r="B76" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15721,7 +15421,7 @@
       </c>
       <c r="C76" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D76" s="2" t="inlineStr">
@@ -15912,11 +15612,7 @@
       </c>
     </row>
     <row r="77">
-      <c r="A77" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A77" s="2" t="inlineStr"/>
       <c r="B77" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -15924,7 +15620,7 @@
       </c>
       <c r="C77" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D77" s="2" t="inlineStr">
@@ -16115,11 +15811,7 @@
       </c>
     </row>
     <row r="78">
-      <c r="A78" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A78" s="2" t="inlineStr"/>
       <c r="B78" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16127,7 +15819,7 @@
       </c>
       <c r="C78" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D78" s="2" t="inlineStr">
@@ -16318,11 +16010,7 @@
       </c>
     </row>
     <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A79" s="2" t="inlineStr"/>
       <c r="B79" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16330,7 +16018,7 @@
       </c>
       <c r="C79" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D79" s="2" t="inlineStr">
@@ -16521,11 +16209,7 @@
       </c>
     </row>
     <row r="80">
-      <c r="A80" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A80" s="2" t="inlineStr"/>
       <c r="B80" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16533,7 +16217,7 @@
       </c>
       <c r="C80" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D80" s="2" t="inlineStr">
@@ -16708,11 +16392,7 @@
       </c>
     </row>
     <row r="81">
-      <c r="A81" s="2" t="inlineStr">
-        <is>
-          <t>TRATADO</t>
-        </is>
-      </c>
+      <c r="A81" s="2" t="inlineStr"/>
       <c r="B81" s="2" t="inlineStr">
         <is>
           <t>111001800414</t>
@@ -16720,7 +16400,7 @@
       </c>
       <c r="C81" s="2" t="inlineStr">
         <is>
-          <t>COLEGIO EL ENSUEÑO (IED)</t>
+          <t>COLEGIO EL ENSUEÑO (IED) - SEDE PRINCIPAL</t>
         </is>
       </c>
       <c r="D81" s="2" t="inlineStr">
